--- a/output/pdf_financials_xlsx/CSTL.P.xlsx
+++ b/output/pdf_financials_xlsx/CSTL.P.xlsx
@@ -3464,7 +3464,7 @@
         <v>-0.015353</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.179388</v>
+        <v>-0.179388</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>0.07348200000000001</v>
@@ -6387,7 +6387,7 @@
         <v>-0.015353</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.179388</v>
+        <v>-0.179388</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CSTL.P.xlsx
+++ b/output/pdf_financials_xlsx/CSTL.P.xlsx
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.033521</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.054418</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.015353</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.020612</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.024929</v>
       </c>
     </row>
     <row r="11">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.033521</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.054418</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.015353</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.020612</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.024929</v>
       </c>
     </row>
     <row r="12">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001118</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.06868299999999999</v>
+        <v>-0.069801</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.06868299999999999</v>
+        <v>-0.069801</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -1437,22 +1437,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.172793</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.12693</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.077538</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.060481</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.046327</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022913</v>
       </c>
     </row>
     <row r="35">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.172793</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.12693</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.077538</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.060481</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.046327</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.022913</v>
       </c>
     </row>
     <row r="37">
@@ -1860,19 +1860,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.12693</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.077538</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.060841</v>
+        <v>0.00036</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.246327</v>
+        <v>0.2</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.322913</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="49">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7284,19 +7284,19 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.033521</v>
+        <v>0.033521</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.054418</v>
+        <v>0.054418</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.015353</v>
+        <v>0.015353</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.020612</v>
+        <v>0.020612</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.024929</v>
+        <v>0.024929</v>
       </c>
     </row>
     <row r="54">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/CSTL.P.xlsx
+++ b/output/pdf_financials_xlsx/CSTL.P.xlsx
@@ -1431,10 +1431,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.151646</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.172793</v>
@@ -1461,10 +1459,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1491,10 +1487,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.151646</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.172793</v>
@@ -1521,10 +1515,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1551,10 +1543,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1581,10 +1571,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1611,10 +1599,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0.00525</v>
@@ -1641,10 +1627,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.00525</v>
@@ -1671,10 +1655,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1701,10 +1683,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1731,10 +1711,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1761,10 +1739,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1791,10 +1767,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1821,10 +1795,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1851,10 +1823,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -1881,10 +1851,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.151646</v>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
@@ -1913,10 +1881,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1943,10 +1909,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1973,10 +1937,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -2003,10 +1965,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -2033,10 +1993,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -2105,10 +2063,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -2135,10 +2091,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -2165,10 +2119,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -2195,10 +2147,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -2225,10 +2175,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -2255,10 +2203,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -2367,10 +2313,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0.004595</v>
@@ -2397,10 +2341,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -2427,10 +2369,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -2457,10 +2397,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -2487,10 +2425,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.0046</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.004595</v>
@@ -2517,10 +2453,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -2547,10 +2481,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -2577,10 +2509,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -2607,10 +2537,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -2637,10 +2565,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -2667,10 +2593,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -2697,10 +2621,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2765,10 +2687,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2795,10 +2715,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2825,10 +2743,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2897,10 +2813,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -2927,10 +2841,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -2957,10 +2869,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -2987,10 +2897,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -3017,10 +2925,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -3129,10 +3035,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.195721</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0</v>
@@ -3159,10 +3063,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -3219,10 +3121,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -3249,10 +3149,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.04641</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.04641</v>
@@ -3279,10 +3177,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -3309,10 +3205,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.147046</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.173448</v>
@@ -3339,10 +3233,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -3369,10 +3261,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.147046</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.173448</v>
@@ -3507,7 +3397,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.00525</v>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
@@ -3657,7 +3547,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>5e-06</v>
+        <v>0.005255</v>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
@@ -4599,7 +4489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5139,10 +5029,8 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="5" t="n">
+        <v>0.147046</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -5326,28 +5214,20 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Current assets</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cash $</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.172793</v>
+          <t>As at December 31, As at December</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -5388,21 +5268,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>Cash 126,930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.00525</v>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.151646</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -5443,21 +5323,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total Assets $</t>
+          <t>Current assets total</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.178043</v>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.151646</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -5498,21 +5378,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Accounts payable $</t>
+          <t>Accounts payable and accrued liabilities 4,705</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AccountsPayable</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.004595</v>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -5548,22 +5428,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Share capital, net of issuance cost (note 6) $</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
+          <t>Share capital 6 195,721</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>0.195721</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -5599,12 +5483,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Contributed surplus 55,110</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5612,13 +5496,13 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
+      <c r="E20" s="5" t="n">
         <v>0.04641</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -5654,26 +5538,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-0.06868299999999999</v>
+          <t>Accumulated deficit (128,606)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>-0.095085</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -5709,26 +5589,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shareholders' equity total</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.173448</v>
+          <t>Nature and continuance of operations</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5764,26 +5640,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders' Equity $</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.178043</v>
+          <t>Year ended December</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -5819,22 +5691,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nature and continuance of operations (Note</t>
+          <t>General and administrative 16,881</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>1e-06</v>
+      <c r="E24" s="5" t="n">
+        <v>0.021814</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -5870,12 +5742,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Approved on Behalf of the Board on April 6,</t>
+          <t>Stock-based compensation 6 8,700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -5884,8 +5756,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>0.00202</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -5916,24 +5790,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Income and comprehensive income</t>
+          <t>Professional fees 7,940</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="5" t="n">
+        <v>0.004588</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5955,34 +5827,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>0.179388</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0.07348200000000001</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Recovery of costs 6</t>
+          <t>Total expenses (33,521)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="5" t="n">
+        <v>-0.026402</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -6004,81 +5878,87 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.1</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss (33,521)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="n">
+        <v>-0.026402</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>0.000105</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.005026</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-0.001704</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0.006458</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.001515</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Income taxes payable</t>
+          <t>Basic and diluted loss per share 7 (0.02)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -6105,29 +5985,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>0.001589</v>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash utilized in operating activities</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6135,46 +6017,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-0.024716</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-0.049392</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>-0.017057</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-0.014154</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.023414</v>
+      <c r="F30" s="5" t="n">
+        <v>0.172793</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>OtherReceivables</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6182,46 +6072,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-0.024716</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>-0.049392</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-0.017057</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-0.014154</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>-0.023414</v>
+      <c r="F31" s="5" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Total Assets $</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6229,46 +6127,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.151646</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.12693</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.077538</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0.060481</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0.046327</v>
+      <c r="F32" s="5" t="n">
+        <v>0.178043</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current liability</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash, end of the year</t>
+          <t>Accounts payable $</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>AccountsPayable</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6276,41 +6182,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.12693</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0.077538</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.060481</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0.046327</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>0.022913</v>
+      <c r="F33" s="5" t="n">
+        <v>0.004595</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.    Functional and presentation currency</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Directors on April</t>
+          <t>Share capital, net of issuance cost (note 6) $</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6319,10 +6233,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>0.195721</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -6339,32 +6251,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>0.002026</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>2.4e-05</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6372,22 +6288,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>-0.033521</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>-0.054418</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.015353</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-0.179388</v>
+      <c r="F35" s="5" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -6398,29 +6320,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Investment in private company</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="5" t="n">
+        <v>-0.06868299999999999</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6437,8 +6361,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>-0.2</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -6449,29 +6375,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.    Functional and presentation currency</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on April</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Shareholders' equity total</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="5" t="n">
+        <v>0.173448</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6483,11 +6411,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>2.8e-05</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -6498,38 +6430,46 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.    Functional and presentation currency</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on February</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders' Equity $</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>2.8e-05</v>
+      <c r="F38" s="5" t="n">
+        <v>0.178043</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6545,23 +6485,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shareholders' equity</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Year ended December</t>
+          <t>Nature and continuance of operations (Note</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6592,27 +6536,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss (33,521)</t>
+          <t>Approved on Behalf of the Board on April 6,</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>-0.026402</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6653,14 +6597,10 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8,700</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Income and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -6686,15 +6626,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J41" s="5" t="n">
+        <v>0.179388</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.07348200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -6705,17 +6641,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GST receivable -</t>
+          <t>Recovery of costs 6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>0.00525</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6737,15 +6675,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J42" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="43">
@@ -6761,7 +6695,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 105</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6769,38 +6703,30 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>5e-06</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G43" s="5" t="n">
+        <v>0.000105</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.005026</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>-0.001704</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.006458</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.001515</v>
       </c>
     </row>
     <row r="44">
@@ -6816,12 +6742,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Net cash utilized in operating activities (24,716)</t>
+          <t>Income taxes payable</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>-0.021147</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6848,10 +6776,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K44" s="5" t="n">
+        <v>0.001589</v>
       </c>
     </row>
     <row r="45">
@@ -6867,42 +6793,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net change in cash (24,716)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>-0.021147</v>
+          <t>Net cash utilized in operating activities</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>-0.024716</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>-0.049392</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.017057</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.014154</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>-0.023414</v>
       </c>
     </row>
     <row r="46">
@@ -6918,46 +6840,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year 151,646</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.172793</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G46" s="5" t="n">
+        <v>-0.024716</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-0.049392</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-0.017057</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-0.014154</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>-0.023414</v>
       </c>
     </row>
     <row r="47">
@@ -6973,46 +6887,38 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash, end of the year 126,930</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>0.151646</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H47" s="5" t="n">
+        <v>0.12693</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.077538</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.060481</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.046327</v>
       </c>
     </row>
     <row r="48">
@@ -7023,47 +6929,43 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.    Functional and presentation currency</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on March 21,</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>0.002022</v>
+          <t>Cash, end of the year</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="5" t="n">
+        <v>0.12693</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.077538</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0.060481</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.046327</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.022913</v>
       </c>
     </row>
     <row r="49">
@@ -7072,18 +6974,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2.    Functional and presentation currency</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>From incorporation on November 8, 2018 to December</t>
+          <t>Directors on April</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.002019</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7100,15 +7010,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J49" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>2.4e-05</v>
       </c>
     </row>
     <row r="50">
@@ -7119,40 +7025,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Issuance of share capital, net of costs                                          206,299</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Net change during the period and cash at December 31,</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0.172793</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.033521</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-0.054418</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.015353</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-0.179388</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -7163,69 +7069,71 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0.029369</v>
+          <t>Investment in private company</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n">
-        <v>0.007939999999999999</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>0.041118</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>0.005284</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>0.009084999999999999</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>0.00525</v>
+        <v>-0.2</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>2.    Functional and presentation currency</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on April</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7236,43 +7144,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n">
-        <v>0.016881</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0.0133</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0.010069</v>
+        <v>0.002025</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0.011527</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>0.019679</v>
+        <v>2.8e-05</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>2.    Functional and presentation currency</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on February</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -7284,42 +7194,40 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.033521</v>
+        <v>0.002023</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.054418</v>
+        <v>0.002024</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.015353</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>0.020612</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>0.024929</v>
+        <v>2.8e-05</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Recovery of costs 6</t>
+          <t>Year ended December</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7341,34 +7249,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>0.1</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Income and comprehensive income before income tax</t>
+          <t>Net loss and comprehensive loss (33,521)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="5" t="n">
+        <v>-0.026402</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7390,32 +7300,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J55" s="5" t="n">
-        <v>0.179388</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>0.075071</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Income tax</t>
+          <t>Stock-based compensation 8,700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7448,35 +7362,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K56" s="5" t="n">
-        <v>0.001589</v>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Income and comprehensive income</t>
+          <t>GST receivable -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.00525</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7498,38 +7412,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n">
-        <v>0.179388</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>0.07348200000000001</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings per share 8</t>
+          <t>Accounts payable and accrued liabilities 105</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>5e-06</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7551,38 +7467,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>9e-08</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>4e-08</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Income (loss) and comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash utilized in operating activities (24,716)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>-0.021147</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7599,11 +7513,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>-0.015353</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>0.179388</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -7614,28 +7532,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 8</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash (24,716)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>-0.021147</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7652,11 +7564,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>9e-08</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -7667,42 +7583,46 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
+          <t>Cash, beginning of the year 151,646</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.172793</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.033521</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>-0.054418</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>-0.015353</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -7718,42 +7638,46 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 7</t>
+          <t>Cash, end of the year 126,930</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.151646</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -7769,22 +7693,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nov. 8, 2018 to</t>
+          <t>2.    Functional and presentation currency</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dec. 31,</t>
+          <t>Standards (“IFRS”) and interpretations adopted by the International Accounting Standards Board. The financial statements were approved by the Board of Directors on March 21,</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.002019</v>
+        <v>0.002022</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7820,31 +7744,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Interest income $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>From incorporation on November 8, 2018 to December</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.001118</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.1e-05</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.002019</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7875,31 +7789,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issuance of share capital, net of costs                                          206,299</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>General and administrative $</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Net change during the period and cash at December 31,</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002019</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.172793</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7940,42 +7848,36 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stock based compensation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
-        <v>0.035832</v>
+        <v>0.029369</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G66" s="5" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.041118</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.005284</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0.009084999999999999</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.00525</v>
       </c>
     </row>
     <row r="67">
@@ -7991,46 +7893,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>-0.06868299999999999</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G67" s="5" t="n">
+        <v>0.016881</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.010069</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>0.011527</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0.019679</v>
       </c>
     </row>
     <row r="68">
@@ -8046,12 +7940,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Income taxes (note 7)</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8064,30 +7958,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>0.033521</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.054418</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.015353</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>0.020612</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0.024929</v>
       </c>
     </row>
     <row r="69">
@@ -8098,21 +7982,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>-0.06868299999999999</v>
+          <t>Recovery of costs 6</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8134,15 +8016,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J69" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="70">
@@ -8153,21 +8031,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>1.066986</v>
+          <t>Income and comprehensive income before income tax</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8189,15 +8065,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J70" s="5" t="n">
+        <v>0.179388</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0.075071</v>
       </c>
     </row>
     <row r="71">
@@ -8208,17 +8080,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>basic and diluted (Note</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>8e-06</v>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8245,10 +8123,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K71" s="5" t="n">
+        <v>0.001589</v>
       </c>
     </row>
     <row r="72">
@@ -8259,48 +8135,847 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Income and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.179388</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0.07348200000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Basic and diluted earnings per share 8</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.015353</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>0.179388</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 8</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>-0.033521</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>-0.054418</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>-0.015353</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 7</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nov. 8, 2018 to</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Dec. 31,</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Interest income $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.001118</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Stock based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>0.035832</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.06868299999999999</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Income taxes (note 7)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.06868299999999999</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding -</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1.066986</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>basic and diluted (Note</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>8e-06</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>Basic and diluted loss per share $</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E87" s="5" t="n">
         <v>5.999999999999999e-08</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
